--- a/C&K.xlsx
+++ b/C&K.xlsx
@@ -663,7 +663,7 @@
     <row r="1" ht="46.8" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>We first met at a cousin’s wedding; ironically, in a room full of laughter, celebration, and love stories just beginning. But despite the setting, it wasn’t love at first sight. Life went on, but eventually brought us back together a year later, this time with a little more intention.</t>
+          <t>We first met at a cousin’s wedding; ironically, in a room full of laughter, celebration, and love stories just beginning. But while love was all around us that day, our own story needed a little more time to unfold. Life went on, but eventually brought us back together a year later, this time with a little more intention.</t>
         </is>
       </c>
     </row>
